--- a/Config/Datas/PCDatas/PCData.xlsx
+++ b/Config/Datas/PCDatas/PCData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\BBQ\Config\Datas\PCDatas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\PCDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2AF7E7D-05C4-4D59-9F66-650E37E314AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB39B1C9-66F8-497F-AEF9-4879113AD0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -144,10 +144,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>wood|wood|wood</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>完成烧烤后</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -197,6 +193,10 @@
   </si>
   <si>
     <t>DV_值,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wood|iron|short</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -596,7 +596,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>21</v>
@@ -722,10 +722,10 @@
         <v>1</v>
       </c>
       <c r="L5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="N5" s="8" t="s">
         <v>26</v>
@@ -746,16 +746,16 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
         <v>36</v>
       </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="I6" t="s">
         <v>12</v>
@@ -778,16 +778,16 @@
         <v>12</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K7" s="5">
         <v>1</v>
       </c>
       <c r="P7" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q7" t="s">
         <v>29</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>30</v>
       </c>
       <c r="S7" s="2"/>
     </row>
@@ -796,16 +796,16 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
         <v>38</v>
       </c>
-      <c r="E11" t="s">
-        <v>39</v>
-      </c>
       <c r="H11" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="I11" t="s">
         <v>12</v>
@@ -822,7 +822,7 @@
         <v>19</v>
       </c>
       <c r="Q11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">

--- a/Config/Datas/PCDatas/PCData.xlsx
+++ b/Config/Datas/PCDatas/PCData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\PCDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB39B1C9-66F8-497F-AEF9-4879113AD0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA07DB8-23CF-4D30-9587-EA5C881591A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Config/Datas/PCDatas/PCData.xlsx
+++ b/Config/Datas/PCDatas/PCData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\PCDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA07DB8-23CF-4D30-9587-EA5C881591A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A4E417-19D8-48B4-A803-7D72C6D062A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Config/Datas/PCDatas/PCData.xlsx
+++ b/Config/Datas/PCDatas/PCData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\PCDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A4E417-19D8-48B4-A803-7D72C6D062A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5977E5-EA94-4C35-AAC7-7C865B10A569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -757,21 +757,6 @@
       <c r="H6" t="s">
         <v>40</v>
       </c>
-      <c r="I6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" s="2">
-        <v>1</v>
-      </c>
-      <c r="P6" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="I7" t="s">
@@ -790,6 +775,23 @@
         <v>29</v>
       </c>
       <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="I8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="P8" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B11">

--- a/Config/Datas/PCDatas/PCData.xlsx
+++ b/Config/Datas/PCDatas/PCData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\PCDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5977E5-EA94-4C35-AAC7-7C865B10A569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B09C78B-2429-407B-9829-0FA0FF08D500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -92,10 +92,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>每日开始系统后</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GA_测试文字</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -188,15 +184,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;被动：&lt;/color&gt;每天开始经营时，额外补充10个食材</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DV_值,10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>wood|iron|short</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;被动：&lt;/color&gt;每次串完串后，抽取两张食材卡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -563,26 +559,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="5" width="9.625" customWidth="1"/>
+    <col min="4" max="5" width="9.58203125" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="16.125" customWidth="1"/>
+    <col min="8" max="8" width="16.08203125" customWidth="1"/>
     <col min="9" max="9" width="13.75" customWidth="1"/>
-    <col min="10" max="10" width="14.375" customWidth="1"/>
-    <col min="11" max="11" width="8.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" customWidth="1"/>
+    <col min="11" max="11" width="8.58203125" style="5" customWidth="1"/>
     <col min="12" max="12" width="7.25" customWidth="1"/>
-    <col min="13" max="13" width="6.875" customWidth="1"/>
-    <col min="14" max="14" width="10.625" customWidth="1"/>
+    <col min="13" max="13" width="6.83203125" customWidth="1"/>
+    <col min="14" max="14" width="10.58203125" customWidth="1"/>
     <col min="15" max="15" width="10.5" customWidth="1"/>
     <col min="16" max="16" width="13.5" customWidth="1"/>
-    <col min="17" max="17" width="14.625" customWidth="1"/>
+    <col min="17" max="17" width="14.58203125" customWidth="1"/>
     <col min="18" max="18" width="17.25" customWidth="1"/>
     <col min="19" max="19" width="18.75" customWidth="1"/>
-    <col min="20" max="20" width="13.375" customWidth="1"/>
+    <col min="20" max="20" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -596,19 +592,19 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="I1" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
@@ -622,7 +618,7 @@
       <c r="S1" s="6"/>
       <c r="T1" s="6"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -642,10 +638,10 @@
         <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>10</v>
@@ -662,7 +658,7 @@
       <c r="S2" s="7"/>
       <c r="T2" s="7"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -689,7 +685,7 @@
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -697,10 +693,10 @@
         <v>11</v>
       </c>
       <c r="J4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>17</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
@@ -709,12 +705,12 @@
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
       <c r="R4" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -722,17 +718,17 @@
         <v>1</v>
       </c>
       <c r="L5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="N5" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O5" s="8"/>
       <c r="P5" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q5" s="8"/>
       <c r="S5" s="3"/>
@@ -741,42 +737,42 @@
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
         <v>35</v>
       </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="I7" t="s">
         <v>12</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K7" s="5">
         <v>1</v>
       </c>
       <c r="P7" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" t="s">
         <v>28</v>
       </c>
-      <c r="Q7" t="s">
-        <v>29</v>
-      </c>
       <c r="S7" s="2"/>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="I8" t="s">
         <v>12</v>
       </c>
@@ -787,33 +783,33 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q8" t="s">
         <v>15</v>
       </c>
-      <c r="Q8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" t="s">
         <v>37</v>
-      </c>
-      <c r="E11" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" t="s">
-        <v>40</v>
       </c>
       <c r="I11" t="s">
         <v>12</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
@@ -821,13 +817,13 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="P11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
